--- a/data_out/country_spreadsheets/Luxembourg.xlsx
+++ b/data_out/country_spreadsheets/Luxembourg.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -619,6 +704,57 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
+        <v>90.15000000000001</v>
+      </c>
+      <c r="X2" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>53.96</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>69.65000000000001</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>32.54</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>195.27</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>171.22</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>186.66</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>222.37</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>52.07</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>214.36</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>66.79000000000001</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
         <v>90.15000000000001</v>
       </c>
     </row>
